--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T06:43:36+00:00</t>
+    <t>2026-08-30T06:48:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T06:48:22+00:00</t>
+    <t>2026-08-30T07:19:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T07:19:06+00:00</t>
+    <t>2026-08-30T09:13:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T09:13:23+00:00</t>
+    <t>2026-08-30T09:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T09:26:51+00:00</t>
+    <t>2026-08-30T09:45:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,19 +57,19 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T09:45:44+00:00</t>
+    <t>2026-08-30T12:16:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>Medizininformatik-Initiative</t>
+    <t>NUM-DIZ</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>Medizininformatik-Initiative (https://www.medizininformatik-initiative.de, office@medizininformatik-initiative.de)</t>
+    <t>NUM-DIZ (https://www.netzwerk-universitaetsmedizin.de)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T12:16:15+00:00</t>
+    <t>2026-08-30T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T12:43:17+00:00</t>
+    <t>2026-08-30T17:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T17:48:45+00:00</t>
+    <t>2026-08-30T18:38:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T18:38:46+00:00</t>
+    <t>2026-08-30T18:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T18:44:43+00:00</t>
+    <t>2026-08-30T19:02:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T19:02:27+00:00</t>
+    <t>2026-08-30T20:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.1/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-30T20:47:31+00:00</t>
+    <t>2026-09-04T12:20:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
